--- a/hr_toolkit/templates/archive_summary_template.xlsx
+++ b/hr_toolkit/templates/archive_summary_template.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="14800"/>
+    <workbookView windowHeight="22140"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>人事档案编号表</t>
   </si>
@@ -144,20 +144,24 @@
   </si>
   <si>
     <t>离职申请单</t>
+  </si>
+  <si>
+    <t>离职时间</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="8">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="0_ "/>
     <numFmt numFmtId="178" formatCode="yyyymmdd"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -169,14 +173,21 @@
       <b/>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -184,14 +195,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -199,7 +203,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -207,14 +211,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -222,7 +226,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -230,7 +234,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -238,7 +242,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -246,7 +250,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -254,14 +258,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -269,7 +273,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -277,7 +281,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -285,14 +289,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -300,42 +304,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -540,7 +544,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -572,6 +576,17 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -690,19 +705,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -711,7 +726,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -723,34 +738,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
@@ -834,10 +849,10 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -846,91 +861,99 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="51">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 29" xfId="49"/>
     <cellStyle name="常规 27" xfId="50"/>
   </cellStyles>
@@ -1417,7 +1440,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr defaultColWidth="8.66964285714286" defaultRowHeight="17.6" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="33.5267857142857" style="1" customWidth="1"/>
@@ -1426,9 +1449,10 @@
     <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="20" style="1" customWidth="1"/>
     <col min="30" max="30" width="51.75" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="25.5" customHeight="1" spans="1:36">
+    <row r="1" ht="25.5" customHeight="1" spans="1:37">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1466,10 +1490,10 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
-      <c r="AJ1" s="12"/>
+      <c r="AJ1" s="4"/>
     </row>
-    <row r="2" customFormat="1" ht="46" customHeight="1" spans="1:36">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="46" customHeight="1" spans="1:37">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3"/>
@@ -1485,139 +1509,143 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="14" t="s">
+      <c r="O2" s="6"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="Z2" s="8"/>
+      <c r="AA2" s="8"/>
+      <c r="AB2" s="8"/>
+      <c r="AC2" s="8"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="11"/>
     </row>
-    <row r="3" customFormat="1" spans="1:36">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:37">
+      <c r="A3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AC3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AD3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AE3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AF3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AG3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AH3" s="6" t="s">
+      <c r="AH3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AI3" s="6" t="s">
+      <c r="AI3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AJ3" s="6" t="s">
+      <c r="AJ3" s="13" t="s">
         <v>38</v>
+      </c>
+      <c r="AK3" s="19" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
